--- a/public/StructureDefinition-pghd-hearing-sensitivity.xlsx
+++ b/public/StructureDefinition-pghd-hearing-sensitivity.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-hearing-sensitivity.xlsx
+++ b/public/StructureDefinition-pghd-hearing-sensitivity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7141" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7141" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -981,6 +981,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6737,7 +6740,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
@@ -6771,7 +6774,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6848,10 +6851,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6968,10 +6971,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7011,7 +7014,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7091,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7208,10 +7211,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7330,13 +7333,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>302</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7454,7 +7457,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>307</v>
@@ -7572,7 +7575,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>309</v>
@@ -7692,7 +7695,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>311</v>
@@ -7737,7 +7740,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7814,10 +7817,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7934,10 +7937,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8054,10 +8057,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8174,10 +8177,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8296,10 +8299,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8418,10 +8421,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8444,19 +8447,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8505,7 +8508,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8520,19 +8523,19 @@
         <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8540,10 +8543,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8566,16 +8569,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8625,7 +8628,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8649,10 +8652,10 @@
         <v>296</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8660,14 +8663,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8686,19 +8689,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8747,7 +8750,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8762,19 +8765,19 @@
         <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8782,14 +8785,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8808,19 +8811,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8869,7 +8872,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8884,19 +8887,19 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8904,10 +8907,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8930,16 +8933,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8989,7 +8992,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9010,13 +9013,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9024,10 +9027,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9050,17 +9053,17 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9112,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9124,19 +9127,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9144,10 +9147,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9170,19 +9173,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9231,7 +9234,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9240,7 +9243,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -9249,27 +9252,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9295,16 +9298,16 @@
         <v>191</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9329,13 +9332,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9353,7 +9356,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9362,7 +9365,7 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -9377,7 +9380,7 @@
         <v>136</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9388,14 +9391,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9417,16 +9420,16 @@
         <v>191</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9451,13 +9454,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9475,7 +9478,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9493,27 +9496,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9536,19 +9539,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9597,7 +9600,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9618,10 +9621,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9632,10 +9635,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9661,13 +9664,13 @@
         <v>191</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9696,10 +9699,10 @@
         <v>291</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9717,7 +9720,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9735,27 +9738,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9781,16 +9784,16 @@
         <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9818,10 +9821,10 @@
         <v>291</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9839,7 +9842,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9860,10 +9863,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9874,10 +9877,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9900,16 +9903,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9959,7 +9962,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9977,27 +9980,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10020,16 +10023,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10079,7 +10082,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10097,27 +10100,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10140,19 +10143,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10201,7 +10204,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10213,7 +10216,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10222,10 +10225,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10236,10 +10239,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10354,10 +10357,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10474,14 +10477,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10503,10 +10506,10 @@
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>142</v>
@@ -10561,7 +10564,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10596,10 +10599,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10622,13 +10625,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10679,7 +10682,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10688,7 +10691,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10700,10 +10703,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10714,10 +10717,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10740,13 +10743,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10797,7 +10800,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10806,7 +10809,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10818,10 +10821,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10832,10 +10835,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10861,16 +10864,16 @@
         <v>191</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10898,10 +10901,10 @@
         <v>117</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10919,7 +10922,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10937,13 +10940,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10954,10 +10957,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10983,16 +10986,16 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -11020,10 +11023,10 @@
         <v>291</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -11041,7 +11044,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11059,13 +11062,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11076,10 +11079,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11102,17 +11105,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11161,7 +11164,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11185,7 +11188,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11196,10 +11199,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11225,10 +11228,10 @@
         <v>206</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11279,7 +11282,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11300,10 +11303,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11314,10 +11317,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11340,16 +11343,16 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11399,7 +11402,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11420,10 +11423,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11434,10 +11437,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11460,16 +11463,16 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11519,7 +11522,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11540,10 +11543,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11554,10 +11557,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11580,19 +11583,19 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11629,7 +11632,7 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11639,7 +11642,7 @@
         <v>199</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11660,10 +11663,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11674,10 +11677,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11792,10 +11795,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11912,14 +11915,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11941,10 +11944,10 @@
         <v>139</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>142</v>
@@ -11999,7 +12002,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12034,10 +12037,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12063,13 +12066,13 @@
         <v>191</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>290</v>
@@ -12121,7 +12124,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>93</v>
@@ -12139,7 +12142,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>296</v>
@@ -12156,10 +12159,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12182,19 +12185,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12243,7 +12246,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12261,27 +12264,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12307,16 +12310,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12341,13 +12344,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12365,7 +12368,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12374,7 +12377,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12389,7 +12392,7 @@
         <v>136</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12400,14 +12403,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12429,16 +12432,16 @@
         <v>191</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12463,13 +12466,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12487,7 +12490,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12505,27 +12508,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12551,16 +12554,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12609,7 +12612,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12630,10 +12633,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12644,13 +12647,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12672,19 +12675,19 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12733,7 +12736,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12754,10 +12757,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12768,10 +12771,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12886,10 +12889,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13006,14 +13009,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13035,10 +13038,10 @@
         <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>142</v>
@@ -13093,7 +13096,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13128,10 +13131,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13157,13 +13160,13 @@
         <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>290</v>
@@ -13215,7 +13218,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>93</v>
@@ -13233,7 +13236,7 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>296</v>
@@ -13250,10 +13253,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13368,10 +13371,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13488,10 +13491,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13610,10 +13613,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13728,10 +13731,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13848,10 +13851,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13896,7 +13899,7 @@
         <v>82</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>82</v>
@@ -13970,10 +13973,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14090,10 +14093,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14133,7 +14136,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>82</v>
@@ -14210,10 +14213,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14330,10 +14333,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14452,10 +14455,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14574,10 +14577,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14600,19 +14603,19 @@
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14649,7 +14652,7 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
@@ -14659,7 +14662,7 @@
         <v>199</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14677,30 +14680,30 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>82</v>
@@ -14722,19 +14725,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14783,7 +14786,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14801,27 +14804,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14936,10 +14939,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15056,10 +15059,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15082,19 +15085,19 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15143,7 +15146,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15164,10 +15167,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15178,10 +15181,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15207,20 +15210,20 @@
         <v>113</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q105" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R105" t="s" s="2">
         <v>82</v>
@@ -15244,10 +15247,10 @@
         <v>182</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15265,7 +15268,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15286,10 +15289,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15300,10 +15303,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15329,14 +15332,14 @@
         <v>206</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15385,7 +15388,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15406,10 +15409,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15420,10 +15423,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15449,14 +15452,14 @@
         <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15466,7 +15469,7 @@
         <v>82</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>82</v>
@@ -15505,7 +15508,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15514,7 +15517,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>105</v>
@@ -15526,10 +15529,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15540,10 +15543,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15569,16 +15572,16 @@
         <v>113</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15588,7 +15591,7 @@
         <v>82</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>82</v>
@@ -15627,7 +15630,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15648,10 +15651,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15662,10 +15665,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15691,16 +15694,16 @@
         <v>191</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15725,13 +15728,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15749,7 +15752,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15758,7 +15761,7 @@
         <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>105</v>
@@ -15773,7 +15776,7 @@
         <v>136</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15784,14 +15787,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15813,16 +15816,16 @@
         <v>191</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15847,13 +15850,13 @@
         <v>82</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15871,7 +15874,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15889,27 +15892,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15935,16 +15938,16 @@
         <v>83</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15993,7 +15996,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16014,10 +16017,10 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -16028,13 +16031,13 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>82</v>
@@ -16056,19 +16059,19 @@
         <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16117,7 +16120,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16138,10 +16141,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16152,10 +16155,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16270,10 +16273,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16390,14 +16393,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -16419,10 +16422,10 @@
         <v>139</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>142</v>
@@ -16477,7 +16480,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16512,10 +16515,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16541,13 +16544,13 @@
         <v>191</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>290</v>
@@ -16599,7 +16602,7 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>93</v>
@@ -16617,7 +16620,7 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>296</v>
@@ -16634,10 +16637,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16752,10 +16755,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16872,10 +16875,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16947,7 +16950,7 @@
         <v>82</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AC119" s="2"/>
       <c r="AD119" t="s" s="2">
@@ -16992,10 +16995,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C120" t="s" s="2">
         <v>305</v>
@@ -17116,10 +17119,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17234,10 +17237,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17354,10 +17357,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17402,7 +17405,7 @@
         <v>82</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>82</v>
@@ -17476,10 +17479,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17596,10 +17599,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17639,7 +17642,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>82</v>
@@ -17716,10 +17719,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17836,10 +17839,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17958,13 +17961,13 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
@@ -18082,10 +18085,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18200,10 +18203,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18320,10 +18323,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18368,7 +18371,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18442,10 +18445,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18562,10 +18565,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18682,10 +18685,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18802,10 +18805,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18924,10 +18927,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19046,10 +19049,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19072,19 +19075,19 @@
         <v>94</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -19121,7 +19124,7 @@
         <v>82</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AC137" s="2"/>
       <c r="AD137" t="s" s="2">
@@ -19131,7 +19134,7 @@
         <v>199</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19149,30 +19152,30 @@
         <v>82</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>82</v>
@@ -19194,19 +19197,19 @@
         <v>94</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -19255,7 +19258,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19273,27 +19276,27 @@
         <v>82</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19408,10 +19411,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19528,10 +19531,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19554,19 +19557,19 @@
         <v>94</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>82</v>
@@ -19615,7 +19618,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19636,10 +19639,10 @@
         <v>82</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>82</v>
@@ -19650,10 +19653,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19679,20 +19682,20 @@
         <v>113</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q142" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R142" t="s" s="2">
         <v>82</v>
@@ -19716,10 +19719,10 @@
         <v>182</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>82</v>
@@ -19737,7 +19740,7 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19758,10 +19761,10 @@
         <v>82</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19772,10 +19775,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19801,14 +19804,14 @@
         <v>206</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
@@ -19857,7 +19860,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19878,10 +19881,10 @@
         <v>82</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>82</v>
@@ -19892,10 +19895,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19921,14 +19924,14 @@
         <v>107</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>82</v>
@@ -19938,7 +19941,7 @@
         <v>82</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>82</v>
@@ -19977,7 +19980,7 @@
         <v>82</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -19986,7 +19989,7 @@
         <v>93</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>105</v>
@@ -19998,10 +20001,10 @@
         <v>82</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>82</v>
@@ -20012,10 +20015,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20041,16 +20044,16 @@
         <v>113</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>82</v>
@@ -20060,7 +20063,7 @@
         <v>82</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>82</v>
@@ -20099,7 +20102,7 @@
         <v>82</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20120,10 +20123,10 @@
         <v>82</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>82</v>
@@ -20134,10 +20137,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20163,16 +20166,16 @@
         <v>191</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>82</v>
@@ -20197,13 +20200,13 @@
         <v>82</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>82</v>
@@ -20221,7 +20224,7 @@
         <v>82</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20230,7 +20233,7 @@
         <v>93</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>105</v>
@@ -20245,7 +20248,7 @@
         <v>136</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>82</v>
@@ -20256,14 +20259,14 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20285,16 +20288,16 @@
         <v>191</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>82</v>
@@ -20319,13 +20322,13 @@
         <v>82</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>82</v>
@@ -20343,7 +20346,7 @@
         <v>82</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20361,27 +20364,27 @@
         <v>82</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20407,16 +20410,16 @@
         <v>83</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>82</v>
@@ -20465,7 +20468,7 @@
         <v>82</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20486,10 +20489,10 @@
         <v>82</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>82</v>
@@ -20500,13 +20503,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>82</v>
@@ -20528,19 +20531,19 @@
         <v>94</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>82</v>
@@ -20589,7 +20592,7 @@
         <v>82</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20610,10 +20613,10 @@
         <v>82</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>82</v>
@@ -20624,10 +20627,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20742,10 +20745,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20862,14 +20865,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20891,10 +20894,10 @@
         <v>139</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>142</v>
@@ -20949,7 +20952,7 @@
         <v>82</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -20984,10 +20987,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21013,13 +21016,13 @@
         <v>191</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O153" t="s" s="2">
         <v>290</v>
@@ -21071,7 +21074,7 @@
         <v>82</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>93</v>
@@ -21089,7 +21092,7 @@
         <v>82</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>296</v>
@@ -21106,10 +21109,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21224,10 +21227,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21344,10 +21347,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21419,7 +21422,7 @@
         <v>82</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AC156" s="2"/>
       <c r="AD156" t="s" s="2">
@@ -21464,10 +21467,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>305</v>
@@ -21588,10 +21591,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21706,10 +21709,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21826,10 +21829,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21874,7 +21877,7 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>82</v>
@@ -21948,10 +21951,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22068,10 +22071,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22111,7 +22114,7 @@
       </c>
       <c r="Q162" s="2"/>
       <c r="R162" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="S162" t="s" s="2">
         <v>82</v>
@@ -22188,10 +22191,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22308,10 +22311,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22430,13 +22433,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>82</v>
@@ -22554,10 +22557,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22672,10 +22675,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22792,10 +22795,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22840,7 +22843,7 @@
         <v>82</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>82</v>
@@ -22914,10 +22917,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23034,10 +23037,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23154,10 +23157,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23274,10 +23277,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23396,10 +23399,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23518,10 +23521,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23544,19 +23547,19 @@
         <v>94</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23593,7 +23596,7 @@
         <v>82</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AC174" s="2"/>
       <c r="AD174" t="s" s="2">
@@ -23603,7 +23606,7 @@
         <v>199</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23621,30 +23624,30 @@
         <v>82</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D175" t="s" s="2">
         <v>82</v>
@@ -23666,19 +23669,19 @@
         <v>94</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
@@ -23727,7 +23730,7 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -23745,27 +23748,27 @@
         <v>82</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP175" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23880,10 +23883,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24000,10 +24003,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24026,19 +24029,19 @@
         <v>94</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>82</v>
@@ -24087,7 +24090,7 @@
         <v>82</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24108,10 +24111,10 @@
         <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -24122,10 +24125,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24151,20 +24154,20 @@
         <v>113</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q179" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="R179" t="s" s="2">
         <v>82</v>
@@ -24188,10 +24191,10 @@
         <v>182</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -24209,7 +24212,7 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24230,10 +24233,10 @@
         <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>82</v>
@@ -24244,10 +24247,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24273,14 +24276,14 @@
         <v>206</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24329,7 +24332,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24350,10 +24353,10 @@
         <v>82</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>82</v>
@@ -24364,10 +24367,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24393,14 +24396,14 @@
         <v>107</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24410,7 +24413,7 @@
         <v>82</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>82</v>
@@ -24449,7 +24452,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24458,7 +24461,7 @@
         <v>93</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>105</v>
@@ -24470,10 +24473,10 @@
         <v>82</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>82</v>
@@ -24484,10 +24487,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24513,16 +24516,16 @@
         <v>113</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>82</v>
@@ -24532,7 +24535,7 @@
         <v>82</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>82</v>
@@ -24571,7 +24574,7 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24592,10 +24595,10 @@
         <v>82</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24606,10 +24609,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24635,16 +24638,16 @@
         <v>191</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>82</v>
@@ -24669,13 +24672,13 @@
         <v>82</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y183" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z183" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>82</v>
@@ -24693,7 +24696,7 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24702,7 +24705,7 @@
         <v>93</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>105</v>
@@ -24717,7 +24720,7 @@
         <v>136</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24728,14 +24731,14 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
@@ -24757,16 +24760,16 @@
         <v>191</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>82</v>
@@ -24791,13 +24794,13 @@
         <v>82</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>82</v>
@@ -24815,7 +24818,7 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -24833,27 +24836,27 @@
         <v>82</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24879,16 +24882,16 @@
         <v>83</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>82</v>
@@ -24937,7 +24940,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24958,10 +24961,10 @@
         <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
